--- a/import/MAXHUB_products.xlsx
+++ b/import/MAXHUB_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0477A5-A0AC-472B-BF32-0B0B8A8CB10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932290D1-5455-4839-B5F2-6269EDBC9F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="6765" yWindow="885" windowWidth="21600" windowHeight="11295" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="172">
   <si>
     <t>Name</t>
   </si>
@@ -88,9 +88,6 @@
     <t>MAXHUB</t>
   </si>
   <si>
-    <t>Interactive Flat Panel</t>
-  </si>
-  <si>
     <t>XBoard V7 Series</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>XBoard V7 T8650.pdf</t>
   </si>
   <si>
-    <t>V6 Series</t>
-  </si>
-  <si>
     <t>V6 Classic Series Zoom Rooms Version</t>
   </si>
   <si>
@@ -223,12 +217,6 @@
     <t>4.1 Sound Channel System: 4.1 system with 4x10W + 20W output for immersive audio.</t>
   </si>
   <si>
-    <t>CMA Series</t>
-  </si>
-  <si>
-    <t>Commercial Display</t>
-  </si>
-  <si>
     <t>MAXHUB CMA Series</t>
   </si>
   <si>
@@ -247,9 +235,6 @@
     <t>MAXHUB CMD Series.pdf</t>
   </si>
   <si>
-    <t>CMD Series</t>
-  </si>
-  <si>
     <t>MAXHUB CMD Series</t>
   </si>
   <si>
@@ -262,9 +247,6 @@
     <t>MAXHUB CMB Series</t>
   </si>
   <si>
-    <t>CMB Series</t>
-  </si>
-  <si>
     <t>MAXHUB CMB Series.png</t>
   </si>
   <si>
@@ -316,9 +298,6 @@
     <t>Boost your conference experience with our premium, large-format DVLED all-in-one solution</t>
   </si>
   <si>
-    <t>LED Display</t>
-  </si>
-  <si>
     <t>MAXHUB Raptor Series V3 Lite</t>
   </si>
   <si>
@@ -329,9 +308,6 @@
   </si>
   <si>
     <t>Raptor Series V3 Lite.pdf</t>
-  </si>
-  <si>
-    <t>Unified Communication</t>
   </si>
   <si>
     <t>All-in-one LED</t>
@@ -470,9 +446,6 @@
     <t>Accessories</t>
   </si>
   <si>
-    <t>Smart Lectern</t>
-  </si>
-  <si>
     <t>SL22MC.pdf</t>
   </si>
   <si>
@@ -497,13 +470,7 @@
     <t>One-click easy for 4K Ultra HD output. Convenient screen sharing for maximized meeting experiences.</t>
   </si>
   <si>
-    <t>Wireless Box</t>
-  </si>
-  <si>
     <t>ไม่มี PDF</t>
-  </si>
-  <si>
-    <t>Wireless Dongle</t>
   </si>
   <si>
     <t>MAXHUB Wireless Screen Sharing Dongle WT15</t>
@@ -559,6 +526,51 @@
   </si>
   <si>
     <t>Panel SP10.pdf</t>
+  </si>
+  <si>
+    <t>ไม่มี pdf</t>
+  </si>
+  <si>
+    <t>no pdf</t>
+  </si>
+  <si>
+    <t>Interactive-Flat-Panel</t>
+  </si>
+  <si>
+    <t>Commercial-Display</t>
+  </si>
+  <si>
+    <t>LED-Display</t>
+  </si>
+  <si>
+    <t>Unified-Communication</t>
+  </si>
+  <si>
+    <t>Smart-Lectern</t>
+  </si>
+  <si>
+    <t>Wireless-Box</t>
+  </si>
+  <si>
+    <t>Wireless-Dongle</t>
+  </si>
+  <si>
+    <t>CMA-Series</t>
+  </si>
+  <si>
+    <t>CMD-Series</t>
+  </si>
+  <si>
+    <t>CMB-Series</t>
+  </si>
+  <si>
+    <t>V6-Series</t>
+  </si>
+  <si>
+    <t>Xboard-V7-Series</t>
+  </si>
+  <si>
+    <t>XBoard -V7-Series</t>
   </si>
 </sst>
 </file>
@@ -606,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -615,22 +627,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
         </top>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -649,7 +659,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H176" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H176" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1" dataCellStyle="Normal">
   <autoFilter ref="A1:H176" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8B000398-16FD-4922-ADD1-EEFE78CEDB7B}" name="Name" dataCellStyle="Normal"/>
@@ -666,7 +676,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B742" totalsRowShown="0" headerRowDxfId="2" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B742" totalsRowShown="0" headerRowDxfId="0" dataCellStyle="Normal">
   <autoFilter ref="A1:B742" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{B6913FB2-003F-4F8F-88B4-A069ABD8343E}" name="ProductName" dataCellStyle="Normal"/>
@@ -1019,7 +1029,7 @@
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,613 +1055,616 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H8" t="s">
         <v>62</v>
       </c>
-      <c r="H7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
         <v>86</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>90</v>
       </c>
-      <c r="D9" t="s">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>96</v>
       </c>
-      <c r="E9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="H12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>98</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" t="s">
         <v>97</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>100</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" t="s">
         <v>97</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
         <v>101</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>104</v>
       </c>
-      <c r="H12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="H14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
         <v>106</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="E15" t="s">
         <v>110</v>
       </c>
-      <c r="H13" t="s">
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="H15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" t="s">
         <v>109</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="H16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" t="s">
         <v>115</v>
       </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="E17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
         <v>121</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" t="s">
-        <v>131</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
         <v>137</v>
       </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>146</v>
-      </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="J21" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
         <v>150</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="H23" t="s">
         <v>149</v>
-      </c>
-      <c r="E22" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" t="s">
-        <v>162</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H24" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>137</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -2293,372 +2306,372 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>56</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
         <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
         <v>71</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>158</v>
+      <c r="A47" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>158</v>
+      <c r="A48" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
